--- a/data/ams_weekly_data/Fossil/business_report_week12.xlsx
+++ b/data/ams_weekly_data/Fossil/business_report_week12.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/Fossil/business_report_week12.xlsx
+++ b/data/ams_weekly_data/Fossil/business_report_week12.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/Fossil/business_report_week12.xlsx
+++ b/data/ams_weekly_data/Fossil/business_report_week12.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,117 +417,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="W1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>

--- a/data/ams_weekly_data/Fossil/business_report_week12.xlsx
+++ b/data/ams_weekly_data/Fossil/business_report_week12.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,117 +429,117 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>SKU</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>(Parent) ASIN</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>(Child) ASIN</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Title</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Sessions - Total - B2B</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Session Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Page Views - Total - B2B</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Page Views Percentage - Total - B2B</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Featured Offer Percentage - B2B</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>units_ordered</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Units Ordered - B2B</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Unit Session Percentage - B2B</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>ordered_product_sales</t>
         </is>
       </c>
-      <c r="U1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Ordered Product Sales - B2B</t>
         </is>
       </c>
-      <c r="V1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items</t>
         </is>
       </c>
-      <c r="W1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>Total Order Items - B2B</t>
         </is>
@@ -752,7 +764,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
@@ -764,7 +776,7 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>11435.59</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -833,7 +845,7 @@
         <v>1</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
@@ -845,7 +857,7 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>58459.32</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -995,7 +1007,7 @@
         <v>1</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
@@ -1007,7 +1019,7 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>20328.81</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1076,7 +1088,7 @@
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="Q8" t="n">
         <v>1</v>
@@ -1088,7 +1100,7 @@
         <v>0.0058</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>408026.27</v>
       </c>
       <c r="U8" t="n">
         <v>11197</v>
@@ -1157,7 +1169,7 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1169,7 +1181,7 @@
         <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>13894.07</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -1319,7 +1331,7 @@
         <v>1</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -1331,7 +1343,7 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>11011.86</v>
       </c>
       <c r="U11" t="n">
         <v>0</v>
@@ -1400,7 +1412,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -1412,7 +1424,7 @@
         <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>69383.05</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -1481,7 +1493,7 @@
         <v>1</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="Q13" t="n">
         <v>1</v>
@@ -1493,7 +1505,7 @@
         <v>0.0047</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>393057.63</v>
       </c>
       <c r="U13" t="n">
         <v>14494</v>
@@ -1562,7 +1574,7 @@
         <v>1</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -1574,7 +1586,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>11011.86</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -1643,7 +1655,7 @@
         <v>1</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
@@ -1655,7 +1667,7 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>10672.88</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -1724,7 +1736,7 @@
         <v>1</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="Q16" t="n">
         <v>6</v>
@@ -1736,7 +1748,7 @@
         <v>0.0522</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>279599.15</v>
       </c>
       <c r="U16" t="n">
         <v>48282</v>
@@ -1805,7 +1817,7 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
@@ -1817,7 +1829,7 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>7709.32</v>
       </c>
       <c r="U17" t="n">
         <v>0</v>
@@ -1886,7 +1898,7 @@
         <v>0.9583</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
@@ -1898,7 +1910,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>88065.25</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1967,7 +1979,7 @@
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
@@ -1979,7 +1991,7 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>68793.22</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -2129,7 +2141,7 @@
         <v>0.9565</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
@@ -2141,7 +2153,7 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>25411.02</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
@@ -2210,7 +2222,7 @@
         <v>1</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
@@ -2222,7 +2234,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>27537.29</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2291,7 +2303,7 @@
         <v>0.9782999999999999</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="n">
         <v>0</v>
@@ -2303,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>33888.98</v>
       </c>
       <c r="U23" t="n">
         <v>0</v>
@@ -2372,7 +2384,7 @@
         <v>1</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
@@ -2384,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>7878.81</v>
       </c>
       <c r="U24" t="n">
         <v>0</v>
@@ -2453,7 +2465,7 @@
         <v>1</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
@@ -2465,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>16607.63</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2615,7 +2627,7 @@
         <v>0.3</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -2627,7 +2639,7 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>7709.32</v>
       </c>
       <c r="U27" t="n">
         <v>0</v>
@@ -2777,7 +2789,7 @@
         <v>0.8571</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="Q29" t="n">
         <v>0</v>
@@ -2789,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>128718.64</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
@@ -3020,7 +3032,7 @@
         <v>0.6667</v>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="n">
         <v>0</v>
@@ -3032,7 +3044,7 @@
         <v>0</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>14232.2</v>
       </c>
       <c r="U32" t="n">
         <v>0</v>
@@ -3101,7 +3113,7 @@
         <v>1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q33" t="n">
         <v>0</v>
@@ -3113,7 +3125,7 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>22025.42</v>
       </c>
       <c r="U33" t="n">
         <v>0</v>
@@ -3182,7 +3194,7 @@
         <v>1</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q34" t="n">
         <v>0</v>
@@ -3194,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>0</v>
+        <v>20757.63</v>
       </c>
       <c r="U34" t="n">
         <v>0</v>
@@ -3263,7 +3275,7 @@
         <v>1</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Q35" t="n">
         <v>1</v>
@@ -3275,7 +3287,7 @@
         <v>0.07140000000000001</v>
       </c>
       <c r="T35" t="n">
-        <v>0</v>
+        <v>88503.39</v>
       </c>
       <c r="U35" t="n">
         <v>9494</v>
@@ -3344,7 +3356,7 @@
         <v>1</v>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q36" t="n">
         <v>0</v>
@@ -3356,7 +3368,7 @@
         <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>0</v>
+        <v>32023.73</v>
       </c>
       <c r="U36" t="n">
         <v>0</v>
@@ -3425,7 +3437,7 @@
         <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
@@ -3437,7 +3449,7 @@
         <v>0</v>
       </c>
       <c r="T37" t="n">
-        <v>0</v>
+        <v>24566.1</v>
       </c>
       <c r="U37" t="n">
         <v>0</v>
@@ -3506,7 +3518,7 @@
         <v>1</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q38" t="n">
         <v>0</v>
@@ -3518,7 +3530,7 @@
         <v>0</v>
       </c>
       <c r="T38" t="n">
-        <v>0</v>
+        <v>22023.73</v>
       </c>
       <c r="U38" t="n">
         <v>0</v>
@@ -3749,7 +3761,7 @@
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
@@ -3761,7 +3773,7 @@
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>0</v>
+        <v>33035.59</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
@@ -3992,7 +4004,7 @@
         <v>1</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q44" t="n">
         <v>0</v>
@@ -4004,7 +4016,7 @@
         <v>0</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>17368.64</v>
       </c>
       <c r="U44" t="n">
         <v>0</v>
@@ -4316,7 +4328,7 @@
         <v>1</v>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q48" t="n">
         <v>0</v>
@@ -4328,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>12751.69</v>
       </c>
       <c r="U48" t="n">
         <v>0</v>
@@ -4478,7 +4490,7 @@
         <v>1</v>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q50" t="n">
         <v>0</v>
@@ -4490,7 +4502,7 @@
         <v>0</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>40669.49</v>
       </c>
       <c r="U50" t="n">
         <v>0</v>
@@ -4559,7 +4571,7 @@
         <v>0</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
@@ -4571,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>9191.530000000001</v>
       </c>
       <c r="U51" t="n">
         <v>0</v>
@@ -4802,7 +4814,7 @@
         <v>1</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
         <v>0</v>
@@ -4814,7 +4826,7 @@
         <v>0</v>
       </c>
       <c r="T54" t="n">
-        <v>0</v>
+        <v>27538.14</v>
       </c>
       <c r="U54" t="n">
         <v>0</v>
@@ -5450,7 +5462,7 @@
         <v>1</v>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q62" t="n">
         <v>0</v>
@@ -5462,7 +5474,7 @@
         <v>0</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>26261.02</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
@@ -5531,7 +5543,7 @@
         <v>0.0435</v>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q63" t="n">
         <v>0</v>
@@ -5543,7 +5555,7 @@
         <v>0</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>6819.49</v>
       </c>
       <c r="U63" t="n">
         <v>0</v>
@@ -5612,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q64" t="n">
         <v>0</v>
@@ -5624,7 +5636,7 @@
         <v>0</v>
       </c>
       <c r="T64" t="n">
-        <v>0</v>
+        <v>26262.71</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
@@ -5693,7 +5705,7 @@
         <v>1</v>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q65" t="n">
         <v>0</v>
@@ -5705,7 +5717,7 @@
         <v>0</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>12283.05</v>
       </c>
       <c r="U65" t="n">
         <v>0</v>
@@ -5855,7 +5867,7 @@
         <v>0</v>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q67" t="n">
         <v>0</v>
@@ -5867,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>11436.44</v>
       </c>
       <c r="U67" t="n">
         <v>0</v>
@@ -6098,7 +6110,7 @@
         <v>1</v>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" t="n">
         <v>0</v>
@@ -6110,7 +6122,7 @@
         <v>0</v>
       </c>
       <c r="T70" t="n">
-        <v>0</v>
+        <v>8599.15</v>
       </c>
       <c r="U70" t="n">
         <v>0</v>
@@ -6179,7 +6191,7 @@
         <v>1</v>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" t="n">
         <v>1</v>
@@ -6191,7 +6203,7 @@
         <v>0.1429</v>
       </c>
       <c r="T71" t="n">
-        <v>0</v>
+        <v>23724.58</v>
       </c>
       <c r="U71" t="n">
         <v>27995</v>
@@ -6503,7 +6515,7 @@
         <v>1</v>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q75" t="n">
         <v>0</v>
@@ -6515,7 +6527,7 @@
         <v>0</v>
       </c>
       <c r="T75" t="n">
-        <v>0</v>
+        <v>46766.95</v>
       </c>
       <c r="U75" t="n">
         <v>0</v>
@@ -6665,7 +6677,7 @@
         <v>0.9091</v>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
@@ -6677,7 +6689,7 @@
         <v>0</v>
       </c>
       <c r="T77" t="n">
-        <v>0</v>
+        <v>22025.42</v>
       </c>
       <c r="U77" t="n">
         <v>0</v>
@@ -6827,7 +6839,7 @@
         <v>1</v>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q79" t="n">
         <v>0</v>
@@ -6839,7 +6851,7 @@
         <v>0</v>
       </c>
       <c r="T79" t="n">
-        <v>0</v>
+        <v>23723.73</v>
       </c>
       <c r="U79" t="n">
         <v>0</v>
@@ -6908,7 +6920,7 @@
         <v>0</v>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q80" t="n">
         <v>0</v>
@@ -6920,7 +6932,7 @@
         <v>0</v>
       </c>
       <c r="T80" t="n">
-        <v>0</v>
+        <v>11435.59</v>
       </c>
       <c r="U80" t="n">
         <v>0</v>
@@ -7394,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q86" t="n">
         <v>0</v>
@@ -7406,7 +7418,7 @@
         <v>0</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>20757.63</v>
       </c>
       <c r="U86" t="n">
         <v>0</v>
@@ -7556,7 +7568,7 @@
         <v>1</v>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q88" t="n">
         <v>0</v>
@@ -7568,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="T88" t="n">
-        <v>0</v>
+        <v>10164.41</v>
       </c>
       <c r="U88" t="n">
         <v>0</v>
@@ -7961,7 +7973,7 @@
         <v>1</v>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q93" t="n">
         <v>0</v>
@@ -7973,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>13554.24</v>
       </c>
       <c r="U93" t="n">
         <v>0</v>
@@ -8366,7 +8378,7 @@
         <v>1</v>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q98" t="n">
         <v>0</v>
@@ -8378,7 +8390,7 @@
         <v>0</v>
       </c>
       <c r="T98" t="n">
-        <v>0</v>
+        <v>11435.59</v>
       </c>
       <c r="U98" t="n">
         <v>0</v>
@@ -8447,7 +8459,7 @@
         <v>1</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q99" t="n">
         <v>1</v>
@@ -8459,7 +8471,7 @@
         <v>0.0625</v>
       </c>
       <c r="T99" t="n">
-        <v>0</v>
+        <v>38972.88</v>
       </c>
       <c r="U99" t="n">
         <v>22994</v>
@@ -8528,7 +8540,7 @@
         <v>1</v>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q100" t="n">
         <v>0</v>
@@ -8540,7 +8552,7 @@
         <v>0</v>
       </c>
       <c r="T100" t="n">
-        <v>0</v>
+        <v>17791.53</v>
       </c>
       <c r="U100" t="n">
         <v>0</v>
@@ -8690,7 +8702,7 @@
         <v>0</v>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q102" t="n">
         <v>0</v>
@@ -8702,7 +8714,7 @@
         <v>0</v>
       </c>
       <c r="T102" t="n">
-        <v>0</v>
+        <v>16944.92</v>
       </c>
       <c r="U102" t="n">
         <v>0</v>
@@ -8933,7 +8945,7 @@
         <v>1</v>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q105" t="n">
         <v>0</v>
@@ -8945,7 +8957,7 @@
         <v>0</v>
       </c>
       <c r="T105" t="n">
-        <v>0</v>
+        <v>10164.41</v>
       </c>
       <c r="U105" t="n">
         <v>0</v>
@@ -9014,7 +9026,7 @@
         <v>0</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
         <v>0</v>
@@ -9026,7 +9038,7 @@
         <v>0</v>
       </c>
       <c r="T106" t="n">
-        <v>0</v>
+        <v>10377.97</v>
       </c>
       <c r="U106" t="n">
         <v>0</v>
@@ -9419,7 +9431,7 @@
         <v>1</v>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q111" t="n">
         <v>0</v>
@@ -9431,7 +9443,7 @@
         <v>0</v>
       </c>
       <c r="T111" t="n">
-        <v>0</v>
+        <v>81325.42</v>
       </c>
       <c r="U111" t="n">
         <v>0</v>
@@ -9743,7 +9755,7 @@
         <v>1</v>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q115" t="n">
         <v>0</v>
@@ -9755,7 +9767,7 @@
         <v>0</v>
       </c>
       <c r="T115" t="n">
-        <v>0</v>
+        <v>18638.98</v>
       </c>
       <c r="U115" t="n">
         <v>0</v>
@@ -10391,7 +10403,7 @@
         <v>0</v>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q123" t="n">
         <v>0</v>
@@ -10403,7 +10415,7 @@
         <v>0</v>
       </c>
       <c r="T123" t="n">
-        <v>0</v>
+        <v>8302.540000000001</v>
       </c>
       <c r="U123" t="n">
         <v>0</v>
@@ -10634,7 +10646,7 @@
         <v>0</v>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q126" t="n">
         <v>0</v>
@@ -10646,7 +10658,7 @@
         <v>0</v>
       </c>
       <c r="T126" t="n">
-        <v>0</v>
+        <v>28466.95</v>
       </c>
       <c r="U126" t="n">
         <v>0</v>
@@ -10796,7 +10808,7 @@
         <v>1</v>
       </c>
       <c r="P128" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q128" t="n">
         <v>0</v>
@@ -10808,7 +10820,7 @@
         <v>0</v>
       </c>
       <c r="T128" t="n">
-        <v>0</v>
+        <v>17368.64</v>
       </c>
       <c r="U128" t="n">
         <v>0</v>
@@ -11363,7 +11375,7 @@
         <v>1</v>
       </c>
       <c r="P135" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q135" t="n">
         <v>0</v>
@@ -11375,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="T135" t="n">
-        <v>0</v>
+        <v>40665.25</v>
       </c>
       <c r="U135" t="n">
         <v>0</v>
@@ -11444,7 +11456,7 @@
         <v>0.4</v>
       </c>
       <c r="P136" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q136" t="n">
         <v>0</v>
@@ -11456,7 +11468,7 @@
         <v>0</v>
       </c>
       <c r="T136" t="n">
-        <v>0</v>
+        <v>27108.47</v>
       </c>
       <c r="U136" t="n">
         <v>0</v>
@@ -12335,7 +12347,7 @@
         <v>1</v>
       </c>
       <c r="P147" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q147" t="n">
         <v>0</v>
@@ -12347,7 +12359,7 @@
         <v>0</v>
       </c>
       <c r="T147" t="n">
-        <v>0</v>
+        <v>10161.02</v>
       </c>
       <c r="U147" t="n">
         <v>0</v>
@@ -12416,7 +12428,7 @@
         <v>1</v>
       </c>
       <c r="P148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q148" t="n">
         <v>0</v>
@@ -12428,7 +12440,7 @@
         <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>0</v>
+        <v>16944.92</v>
       </c>
       <c r="U148" t="n">
         <v>0</v>
@@ -12578,7 +12590,7 @@
         <v>1</v>
       </c>
       <c r="P150" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q150" t="n">
         <v>0</v>
@@ -12590,7 +12602,7 @@
         <v>0</v>
       </c>
       <c r="T150" t="n">
-        <v>0</v>
+        <v>80049.14999999999</v>
       </c>
       <c r="U150" t="n">
         <v>0</v>
@@ -13712,7 +13724,7 @@
         <v>0</v>
       </c>
       <c r="P164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q164" t="n">
         <v>0</v>
@@ -13724,7 +13736,7 @@
         <v>0</v>
       </c>
       <c r="T164" t="n">
-        <v>0</v>
+        <v>14531.36</v>
       </c>
       <c r="U164" t="n">
         <v>0</v>
@@ -13793,7 +13805,7 @@
         <v>0</v>
       </c>
       <c r="P165" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q165" t="n">
         <v>0</v>
@@ -13805,7 +13817,7 @@
         <v>0</v>
       </c>
       <c r="T165" t="n">
-        <v>0</v>
+        <v>11433.05</v>
       </c>
       <c r="U165" t="n">
         <v>0</v>
@@ -14036,7 +14048,7 @@
         <v>1</v>
       </c>
       <c r="P168" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q168" t="n">
         <v>0</v>
@@ -14048,7 +14060,7 @@
         <v>0</v>
       </c>
       <c r="T168" t="n">
-        <v>0</v>
+        <v>8599.15</v>
       </c>
       <c r="U168" t="n">
         <v>0</v>
@@ -14117,7 +14129,7 @@
         <v>1</v>
       </c>
       <c r="P169" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q169" t="n">
         <v>0</v>
@@ -14129,7 +14141,7 @@
         <v>0</v>
       </c>
       <c r="T169" t="n">
-        <v>0</v>
+        <v>8599.15</v>
       </c>
       <c r="U169" t="n">
         <v>0</v>
@@ -14198,7 +14210,7 @@
         <v>1</v>
       </c>
       <c r="P170" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q170" t="n">
         <v>0</v>
@@ -14210,7 +14222,7 @@
         <v>0</v>
       </c>
       <c r="T170" t="n">
-        <v>0</v>
+        <v>11435.59</v>
       </c>
       <c r="U170" t="n">
         <v>0</v>
@@ -14279,7 +14291,7 @@
         <v>1</v>
       </c>
       <c r="P171" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q171" t="n">
         <v>0</v>
@@ -14291,7 +14303,7 @@
         <v>0</v>
       </c>
       <c r="T171" t="n">
-        <v>0</v>
+        <v>20326.27</v>
       </c>
       <c r="U171" t="n">
         <v>0</v>
@@ -14360,7 +14372,7 @@
         <v>1</v>
       </c>
       <c r="P172" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q172" t="n">
         <v>0</v>
@@ -14372,7 +14384,7 @@
         <v>0</v>
       </c>
       <c r="T172" t="n">
-        <v>0</v>
+        <v>17368.64</v>
       </c>
       <c r="U172" t="n">
         <v>0</v>
@@ -14522,7 +14534,7 @@
         <v>1</v>
       </c>
       <c r="P174" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q174" t="n">
         <v>0</v>
@@ -14534,7 +14546,7 @@
         <v>0</v>
       </c>
       <c r="T174" t="n">
-        <v>0</v>
+        <v>22872.88</v>
       </c>
       <c r="U174" t="n">
         <v>0</v>
@@ -14603,7 +14615,7 @@
         <v>1</v>
       </c>
       <c r="P175" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q175" t="n">
         <v>1</v>
@@ -14615,7 +14627,7 @@
         <v>1</v>
       </c>
       <c r="T175" t="n">
-        <v>0</v>
+        <v>19487.29</v>
       </c>
       <c r="U175" t="n">
         <v>22995</v>
@@ -15089,7 +15101,7 @@
         <v>0.6</v>
       </c>
       <c r="P181" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q181" t="n">
         <v>0</v>
@@ -15101,7 +15113,7 @@
         <v>0</v>
       </c>
       <c r="T181" t="n">
-        <v>0</v>
+        <v>7116.1</v>
       </c>
       <c r="U181" t="n">
         <v>0</v>
@@ -15332,7 +15344,7 @@
         <v>0.75</v>
       </c>
       <c r="P184" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q184" t="n">
         <v>0</v>
@@ -15344,7 +15356,7 @@
         <v>0</v>
       </c>
       <c r="T184" t="n">
-        <v>0</v>
+        <v>16521.19</v>
       </c>
       <c r="U184" t="n">
         <v>0</v>
@@ -15575,7 +15587,7 @@
         <v>1</v>
       </c>
       <c r="P187" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q187" t="n">
         <v>0</v>
@@ -15587,7 +15599,7 @@
         <v>0</v>
       </c>
       <c r="T187" t="n">
-        <v>0</v>
+        <v>50834.75</v>
       </c>
       <c r="U187" t="n">
         <v>0</v>
@@ -15656,7 +15668,7 @@
         <v>0.8788</v>
       </c>
       <c r="P188" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q188" t="n">
         <v>0</v>
@@ -15668,7 +15680,7 @@
         <v>0</v>
       </c>
       <c r="T188" t="n">
-        <v>0</v>
+        <v>73200</v>
       </c>
       <c r="U188" t="n">
         <v>0</v>
@@ -15737,7 +15749,7 @@
         <v>0.541</v>
       </c>
       <c r="P189" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q189" t="n">
         <v>0</v>
@@ -15749,7 +15761,7 @@
         <v>0</v>
       </c>
       <c r="T189" t="n">
-        <v>0</v>
+        <v>67771.19</v>
       </c>
       <c r="U189" t="n">
         <v>0</v>
@@ -16223,7 +16235,7 @@
         <v>1</v>
       </c>
       <c r="P195" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q195" t="n">
         <v>0</v>
@@ -16235,7 +16247,7 @@
         <v>0</v>
       </c>
       <c r="T195" t="n">
-        <v>0</v>
+        <v>9744.07</v>
       </c>
       <c r="U195" t="n">
         <v>0</v>
@@ -16385,7 +16397,7 @@
         <v>0</v>
       </c>
       <c r="P197" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q197" t="n">
         <v>0</v>
@@ -16397,7 +16409,7 @@
         <v>0</v>
       </c>
       <c r="T197" t="n">
-        <v>0</v>
+        <v>9192.370000000001</v>
       </c>
       <c r="U197" t="n">
         <v>0</v>
@@ -16790,7 +16802,7 @@
         <v>1</v>
       </c>
       <c r="P202" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q202" t="n">
         <v>0</v>
@@ -16802,7 +16814,7 @@
         <v>0</v>
       </c>
       <c r="T202" t="n">
-        <v>0</v>
+        <v>40662.71</v>
       </c>
       <c r="U202" t="n">
         <v>0</v>
@@ -16871,7 +16883,7 @@
         <v>0.8</v>
       </c>
       <c r="P203" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q203" t="n">
         <v>1</v>
@@ -16883,7 +16895,7 @@
         <v>0.1667</v>
       </c>
       <c r="T203" t="n">
-        <v>0</v>
+        <v>27110.17</v>
       </c>
       <c r="U203" t="n">
         <v>15995</v>
@@ -17438,7 +17450,7 @@
         <v>1</v>
       </c>
       <c r="P210" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q210" t="n">
         <v>0</v>
@@ -17450,7 +17462,7 @@
         <v>0</v>
       </c>
       <c r="T210" t="n">
-        <v>0</v>
+        <v>11012.71</v>
       </c>
       <c r="U210" t="n">
         <v>0</v>
@@ -17519,7 +17531,7 @@
         <v>1</v>
       </c>
       <c r="P211" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q211" t="n">
         <v>0</v>
@@ -17531,7 +17543,7 @@
         <v>0</v>
       </c>
       <c r="T211" t="n">
-        <v>0</v>
+        <v>24566.1</v>
       </c>
       <c r="U211" t="n">
         <v>0</v>
@@ -17600,7 +17612,7 @@
         <v>1</v>
       </c>
       <c r="P212" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q212" t="n">
         <v>0</v>
@@ -17612,7 +17624,7 @@
         <v>0</v>
       </c>
       <c r="T212" t="n">
-        <v>0</v>
+        <v>24566.1</v>
       </c>
       <c r="U212" t="n">
         <v>0</v>
@@ -17681,7 +17693,7 @@
         <v>0.9697</v>
       </c>
       <c r="P213" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q213" t="n">
         <v>1</v>
@@ -17693,7 +17705,7 @@
         <v>0.0244</v>
       </c>
       <c r="T213" t="n">
-        <v>0</v>
+        <v>40662.71</v>
       </c>
       <c r="U213" t="n">
         <v>15994</v>
@@ -17762,7 +17774,7 @@
         <v>1</v>
       </c>
       <c r="P214" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q214" t="n">
         <v>0</v>
@@ -17774,7 +17786,7 @@
         <v>0</v>
       </c>
       <c r="T214" t="n">
-        <v>0</v>
+        <v>10844.07</v>
       </c>
       <c r="U214" t="n">
         <v>0</v>
@@ -18005,7 +18017,7 @@
         <v>1</v>
       </c>
       <c r="P217" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q217" t="n">
         <v>0</v>
@@ -18017,7 +18029,7 @@
         <v>0</v>
       </c>
       <c r="T217" t="n">
-        <v>0</v>
+        <v>13555.08</v>
       </c>
       <c r="U217" t="n">
         <v>0</v>
@@ -18086,7 +18098,7 @@
         <v>1</v>
       </c>
       <c r="P218" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q218" t="n">
         <v>0</v>
@@ -18098,7 +18110,7 @@
         <v>0</v>
       </c>
       <c r="T218" t="n">
-        <v>0</v>
+        <v>27110.17</v>
       </c>
       <c r="U218" t="n">
         <v>0</v>
@@ -18248,7 +18260,7 @@
         <v>0</v>
       </c>
       <c r="P220" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q220" t="n">
         <v>0</v>
@@ -18260,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="T220" t="n">
-        <v>0</v>
+        <v>21944.07</v>
       </c>
       <c r="U220" t="n">
         <v>0</v>
@@ -18653,7 +18665,7 @@
         <v>0</v>
       </c>
       <c r="P225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q225" t="n">
         <v>0</v>
@@ -18665,7 +18677,7 @@
         <v>0</v>
       </c>
       <c r="T225" t="n">
-        <v>0</v>
+        <v>12158.47</v>
       </c>
       <c r="U225" t="n">
         <v>0</v>
@@ -19058,7 +19070,7 @@
         <v>0</v>
       </c>
       <c r="P230" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q230" t="n">
         <v>0</v>
@@ -19070,7 +19082,7 @@
         <v>0</v>
       </c>
       <c r="T230" t="n">
-        <v>0</v>
+        <v>22871.19</v>
       </c>
       <c r="U230" t="n">
         <v>0</v>
@@ -19625,7 +19637,7 @@
         <v>0.1509</v>
       </c>
       <c r="P237" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q237" t="n">
         <v>0</v>
@@ -19637,7 +19649,7 @@
         <v>0</v>
       </c>
       <c r="T237" t="n">
-        <v>0</v>
+        <v>24567.8</v>
       </c>
       <c r="U237" t="n">
         <v>0</v>
@@ -19706,7 +19718,7 @@
         <v>0.5</v>
       </c>
       <c r="P238" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q238" t="n">
         <v>0</v>
@@ -19718,7 +19730,7 @@
         <v>0</v>
       </c>
       <c r="T238" t="n">
-        <v>0</v>
+        <v>49135.59</v>
       </c>
       <c r="U238" t="n">
         <v>0</v>
@@ -19868,7 +19880,7 @@
         <v>0</v>
       </c>
       <c r="P240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q240" t="n">
         <v>0</v>
@@ -19880,7 +19892,7 @@
         <v>0</v>
       </c>
       <c r="T240" t="n">
-        <v>0</v>
+        <v>10588.14</v>
       </c>
       <c r="U240" t="n">
         <v>0</v>
@@ -20273,7 +20285,7 @@
         <v>0</v>
       </c>
       <c r="P245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q245" t="n">
         <v>0</v>
@@ -20285,7 +20297,7 @@
         <v>0</v>
       </c>
       <c r="T245" t="n">
-        <v>0</v>
+        <v>15250</v>
       </c>
       <c r="U245" t="n">
         <v>0</v>
@@ -20921,7 +20933,7 @@
         <v>0.9677</v>
       </c>
       <c r="P253" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q253" t="n">
         <v>0</v>
@@ -20933,7 +20945,7 @@
         <v>0</v>
       </c>
       <c r="T253" t="n">
-        <v>0</v>
+        <v>33888.14</v>
       </c>
       <c r="U253" t="n">
         <v>0</v>
@@ -21002,7 +21014,7 @@
         <v>0</v>
       </c>
       <c r="P254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q254" t="n">
         <v>0</v>
@@ -21014,7 +21026,7 @@
         <v>0</v>
       </c>
       <c r="T254" t="n">
-        <v>0</v>
+        <v>13555.08</v>
       </c>
       <c r="U254" t="n">
         <v>0</v>
@@ -21326,7 +21338,7 @@
         <v>1</v>
       </c>
       <c r="P258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q258" t="n">
         <v>0</v>
@@ -21338,7 +21350,7 @@
         <v>0</v>
       </c>
       <c r="T258" t="n">
-        <v>0</v>
+        <v>41515.25</v>
       </c>
       <c r="U258" t="n">
         <v>0</v>
@@ -22460,7 +22472,7 @@
         <v>1</v>
       </c>
       <c r="P272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q272" t="n">
         <v>0</v>
@@ -22472,7 +22484,7 @@
         <v>0</v>
       </c>
       <c r="T272" t="n">
-        <v>0</v>
+        <v>11436.44</v>
       </c>
       <c r="U272" t="n">
         <v>0</v>
@@ -22703,7 +22715,7 @@
         <v>0</v>
       </c>
       <c r="P275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q275" t="n">
         <v>0</v>
@@ -22715,7 +22727,7 @@
         <v>0</v>
       </c>
       <c r="T275" t="n">
-        <v>0</v>
+        <v>13978.81</v>
       </c>
       <c r="U275" t="n">
         <v>0</v>
@@ -22946,7 +22958,7 @@
         <v>1</v>
       </c>
       <c r="P278" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q278" t="n">
         <v>0</v>
@@ -22958,7 +22970,7 @@
         <v>0</v>
       </c>
       <c r="T278" t="n">
-        <v>0</v>
+        <v>40661.02</v>
       </c>
       <c r="U278" t="n">
         <v>0</v>
@@ -23189,7 +23201,7 @@
         <v>1</v>
       </c>
       <c r="P281" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q281" t="n">
         <v>0</v>
@@ -23201,7 +23213,7 @@
         <v>0</v>
       </c>
       <c r="T281" t="n">
-        <v>0</v>
+        <v>10165.25</v>
       </c>
       <c r="U281" t="n">
         <v>0</v>
@@ -23270,7 +23282,7 @@
         <v>0</v>
       </c>
       <c r="P282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q282" t="n">
         <v>0</v>
@@ -23282,7 +23294,7 @@
         <v>0</v>
       </c>
       <c r="T282" t="n">
-        <v>0</v>
+        <v>10165.25</v>
       </c>
       <c r="U282" t="n">
         <v>0</v>
@@ -23756,7 +23768,7 @@
         <v>1</v>
       </c>
       <c r="P288" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q288" t="n">
         <v>0</v>
@@ -23768,7 +23780,7 @@
         <v>0</v>
       </c>
       <c r="T288" t="n">
-        <v>0</v>
+        <v>13555.08</v>
       </c>
       <c r="U288" t="n">
         <v>0</v>
@@ -24080,7 +24092,7 @@
         <v>1</v>
       </c>
       <c r="P292" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q292" t="n">
         <v>0</v>
@@ -24092,7 +24104,7 @@
         <v>0</v>
       </c>
       <c r="T292" t="n">
-        <v>0</v>
+        <v>34309.32</v>
       </c>
       <c r="U292" t="n">
         <v>0</v>
@@ -24161,7 +24173,7 @@
         <v>1</v>
       </c>
       <c r="P293" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q293" t="n">
         <v>0</v>
@@ -24173,7 +24185,7 @@
         <v>0</v>
       </c>
       <c r="T293" t="n">
-        <v>0</v>
+        <v>20330.51</v>
       </c>
       <c r="U293" t="n">
         <v>0</v>
@@ -24242,7 +24254,7 @@
         <v>1</v>
       </c>
       <c r="P294" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="Q294" t="n">
         <v>0</v>
@@ -24254,7 +24266,7 @@
         <v>0</v>
       </c>
       <c r="T294" t="n">
-        <v>0</v>
+        <v>57182.2</v>
       </c>
       <c r="U294" t="n">
         <v>0</v>
@@ -24485,7 +24497,7 @@
         <v>0.8333</v>
       </c>
       <c r="P297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q297" t="n">
         <v>0</v>
@@ -24497,7 +24509,7 @@
         <v>0</v>
       </c>
       <c r="T297" t="n">
-        <v>0</v>
+        <v>13555.08</v>
       </c>
       <c r="U297" t="n">
         <v>0</v>
@@ -25052,7 +25064,7 @@
         <v>0</v>
       </c>
       <c r="P304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q304" t="n">
         <v>0</v>
@@ -25064,7 +25076,7 @@
         <v>0</v>
       </c>
       <c r="T304" t="n">
-        <v>0</v>
+        <v>12283.9</v>
       </c>
       <c r="U304" t="n">
         <v>0</v>
@@ -25943,7 +25955,7 @@
         <v>0</v>
       </c>
       <c r="P315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q315" t="n">
         <v>0</v>
@@ -25955,7 +25967,7 @@
         <v>0</v>
       </c>
       <c r="T315" t="n">
-        <v>0</v>
+        <v>12283.9</v>
       </c>
       <c r="U315" t="n">
         <v>0</v>
@@ -27320,7 +27332,7 @@
         <v>0</v>
       </c>
       <c r="P332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q332" t="n">
         <v>0</v>
@@ -27332,7 +27344,7 @@
         <v>0</v>
       </c>
       <c r="T332" t="n">
-        <v>0</v>
+        <v>11436.44</v>
       </c>
       <c r="U332" t="n">
         <v>0</v>
